--- a/01-进度计划/月度计划表/2026.09/月度工作计划表_模板v2_段伟处.xlsx
+++ b/01-进度计划/月度计划表/2026.09/月度工作计划表_模板v2_段伟处.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mrseven\Desktop\总经办文档\01-进度计划\月度计划表\2026.09\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7695" activeTab="1"/>
+    <workbookView windowWidth="23150" windowHeight="14080" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="月度计划明细表" sheetId="1" r:id="rId1"/>
@@ -186,6 +186,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FF1F4E79"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>江西柯美纸业</t>
     </r>
     <r>
@@ -266,7 +273,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -300,7 +307,25 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF1F4E79"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1020,137 +1045,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1158,12 +1183,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1171,18 +1202,24 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1198,54 +1235,75 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="58" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="58" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1258,6 +1316,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1266,6 +1327,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1665,518 +1729,518 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6333333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.6333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6363636363636" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.6363636363636" style="1" customWidth="1"/>
     <col min="4" max="4" width="44" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5416666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.3666666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.4583333333333" style="1" customWidth="1"/>
-    <col min="8" max="11" width="14.6333333333333" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5416666666667" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5416666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5454545454545" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.3636363636364" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.4545454545455" style="1" customWidth="1"/>
+    <col min="8" max="11" width="14.6363636363636" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5454545454545" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5454545454545" style="1" customWidth="1"/>
     <col min="14" max="14" width="12" style="1" customWidth="1"/>
     <col min="15" max="15" width="30" style="1" customWidth="1"/>
-    <col min="16" max="16" width="60.0916666666667" style="1" customWidth="1"/>
+    <col min="16" max="16" width="60.0909090909091" style="1" customWidth="1"/>
     <col min="17" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:16">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="7"/>
     </row>
     <row r="2" ht="23" customHeight="1" spans="1:16">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="8" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="10" t="s">
+      <c r="F2" s="12"/>
+      <c r="G2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="11"/>
-      <c r="I2" s="10" t="s">
+      <c r="H2" s="14"/>
+      <c r="I2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="11"/>
-      <c r="K2" s="8" t="s">
+      <c r="J2" s="14"/>
+      <c r="K2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="9"/>
-      <c r="M2" s="12" t="s">
+      <c r="L2" s="12"/>
+      <c r="M2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="13"/>
-      <c r="O2" s="12" t="s">
+      <c r="N2" s="17"/>
+      <c r="O2" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="P2" s="18" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:16">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="J3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="K3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="16" t="s">
+      <c r="L3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="M3" s="16" t="s">
+      <c r="M3" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="N3" s="16" t="s">
+      <c r="N3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="16" t="s">
+      <c r="O3" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="17" t="s">
+      <c r="P3" s="22" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" ht="31" customHeight="1" spans="1:16">
-      <c r="A4" s="18">
+      <c r="A4" s="23">
         <v>1</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="21">
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="27">
         <v>46249</v>
       </c>
-      <c r="J4" s="21"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="21">
+      <c r="J4" s="27"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="27">
         <v>46264</v>
       </c>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="23"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="29"/>
     </row>
     <row r="5" ht="31" customHeight="1" spans="1:16">
-      <c r="A5" s="18">
+      <c r="A5" s="23">
         <v>2</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21">
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27">
         <v>46257</v>
       </c>
-      <c r="L5" s="21">
+      <c r="L5" s="27">
         <v>46263</v>
       </c>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="23"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="29"/>
     </row>
     <row r="6" ht="31" customHeight="1" spans="1:16">
-      <c r="A6" s="18">
+      <c r="A6" s="23">
         <v>3</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21">
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27">
         <v>46249</v>
       </c>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="21">
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="27">
         <v>46264</v>
       </c>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="23"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="29"/>
     </row>
     <row r="7" ht="31" customHeight="1" spans="1:16">
-      <c r="A7" s="18">
+      <c r="A7" s="23">
         <v>4</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="21">
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="27">
         <v>46249</v>
       </c>
-      <c r="J7" s="21"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="23"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="29"/>
     </row>
     <row r="8" ht="31" customHeight="1" spans="1:16">
-      <c r="A8" s="18">
+      <c r="A8" s="23">
         <v>5</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="27">
         <v>46235</v>
       </c>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="21">
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="27">
         <v>46264</v>
       </c>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="23"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="29"/>
     </row>
     <row r="9" ht="31" customHeight="1" spans="1:16">
-      <c r="A9" s="18">
+      <c r="A9" s="23">
         <v>6</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="27">
         <v>46235</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="27">
         <v>46238</v>
       </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="22"/>
-      <c r="P9" s="23"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="29"/>
     </row>
     <row r="10" ht="31" customHeight="1" spans="1:16">
-      <c r="A10" s="18">
+      <c r="A10" s="23">
         <v>7</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="27">
         <v>46239</v>
       </c>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21">
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27">
         <v>46256</v>
       </c>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="23"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="29"/>
     </row>
     <row r="11" ht="31" customHeight="1" spans="1:16">
-      <c r="A11" s="18">
+      <c r="A11" s="23">
         <v>8</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="27">
         <v>46235</v>
       </c>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="21">
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="27">
         <v>46249</v>
       </c>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="23"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="29"/>
     </row>
     <row r="12" ht="31" customHeight="1" spans="1:16">
-      <c r="A12" s="24">
+      <c r="A12" s="30">
         <v>9</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="27">
         <v>46235</v>
       </c>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="21">
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="27">
         <v>46249</v>
       </c>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="25"/>
-      <c r="O12" s="26"/>
-      <c r="P12" s="27"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="32"/>
+      <c r="P12" s="33"/>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A13" s="28"/>
+      <c r="A13" s="34"/>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A14" s="29"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
+      <c r="A14" s="36"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
     </row>
     <row r="16" ht="32" customHeight="1" spans="1:16">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:10">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="33" t="s">
+      <c r="E17" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="34"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="33" t="s">
+      <c r="F17" s="45"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="I17" s="34"/>
-      <c r="J17" s="35"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="46"/>
     </row>
     <row r="18" ht="32" customHeight="1" spans="1:10">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36" t="s">
+      <c r="A18" s="47"/>
+      <c r="B18" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="C18" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="36" t="s">
+      <c r="D18" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="37" t="s">
+      <c r="E18" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="38"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="39"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="50"/>
+      <c r="J18" s="51"/>
     </row>
     <row r="19" ht="32" customHeight="1" spans="1:10">
-      <c r="A19" s="36"/>
-      <c r="B19" s="36" t="s">
+      <c r="A19" s="47"/>
+      <c r="B19" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="36" t="s">
+      <c r="D19" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="E19" s="37" t="s">
+      <c r="E19" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="38"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="39"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="51"/>
     </row>
     <row r="20" ht="32" customHeight="1" spans="1:10">
-      <c r="A20" s="36"/>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="37"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="39"/>
+      <c r="A20" s="47"/>
+      <c r="B20" s="47"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="51"/>
     </row>
     <row r="21" ht="32" customHeight="1" spans="1:10">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="37"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="39"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="51"/>
     </row>
     <row r="22" ht="32" customHeight="1" spans="1:10">
-      <c r="A22" s="36"/>
-      <c r="B22" s="36"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="39"/>
+      <c r="A22" s="47"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="51"/>
     </row>
     <row r="23" ht="32" customHeight="1"/>
   </sheetData>
@@ -2223,7 +2287,7 @@
     <dataValidation type="list" allowBlank="1" sqref="N4:N12">
       <formula1>"未开始,进行中,已完成,滞后"</formula1>
     </dataValidation>
-    <dataValidation sqref="E13:F14 E4:L12 E16:F22"/>
+    <dataValidation sqref="E4:L12 E13:F14 E16:F22"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" useFirstPageNumber="1"/>
@@ -2238,612 +2302,611 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6333333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.6333333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="44" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5416666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.3666666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.4583333333333" style="1" customWidth="1"/>
-    <col min="8" max="11" width="14.6333333333333" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5416666666667" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5416666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6181818181818" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.8727272727273" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9.72727272727273" style="3" customWidth="1"/>
+    <col min="6" max="12" width="10.4545454545455" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5454545454545" style="1" customWidth="1"/>
     <col min="14" max="14" width="12" style="1" customWidth="1"/>
     <col min="15" max="15" width="30" style="1" customWidth="1"/>
-    <col min="16" max="16" width="60.0916666666667" style="1" customWidth="1"/>
+    <col min="16" max="16" width="60.0909090909091" style="1" customWidth="1"/>
     <col min="17" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="36" customHeight="1" spans="1:16">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="7"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="23" customHeight="1" spans="1:16">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="8" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="10" t="s">
+      <c r="F2" s="12"/>
+      <c r="G2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="11"/>
-      <c r="I2" s="10" t="s">
+      <c r="H2" s="14"/>
+      <c r="I2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="11"/>
-      <c r="K2" s="8" t="s">
+      <c r="J2" s="14"/>
+      <c r="K2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="9"/>
-      <c r="M2" s="12" t="s">
+      <c r="L2" s="12"/>
+      <c r="M2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="13"/>
-      <c r="O2" s="12" t="s">
+      <c r="N2" s="17"/>
+      <c r="O2" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="P2" s="18" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="22" customHeight="1" spans="1:16">
-      <c r="A3" s="15" t="s">
+    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:16">
+      <c r="A3" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="J3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="K3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="16" t="s">
+      <c r="L3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="M3" s="16" t="s">
+      <c r="M3" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="N3" s="16" t="s">
+      <c r="N3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="16" t="s">
+      <c r="O3" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="17" t="s">
+      <c r="P3" s="22" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="31" customHeight="1" spans="1:16">
-      <c r="A4" s="18">
+      <c r="A4" s="23">
         <v>1</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="23"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="29"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="31" customHeight="1" spans="1:16">
-      <c r="A5" s="18">
+      <c r="A5" s="23">
         <v>2</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="26">
         <v>46266</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="27">
         <v>46272</v>
       </c>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="23"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="29"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="31" customHeight="1" spans="1:16">
-      <c r="A6" s="18">
+      <c r="A6" s="23">
         <v>3</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="26">
         <v>46266</v>
       </c>
-      <c r="F6" s="19"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="21">
+      <c r="F6" s="24"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="27">
         <v>46295</v>
       </c>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="23"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="29"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="31" customHeight="1" spans="1:16">
-      <c r="A7" s="18">
+      <c r="A7" s="23">
         <v>4</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="26">
         <v>46266</v>
       </c>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="21">
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="27">
         <v>46295</v>
       </c>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="23"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="29"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="31" customHeight="1" spans="1:16">
-      <c r="A8" s="18">
+      <c r="A8" s="23">
         <v>5</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="21"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="21">
+      <c r="E8" s="26"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="27">
         <v>46280</v>
       </c>
-      <c r="J8" s="21"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="21">
+      <c r="J8" s="27"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="27">
         <v>46295</v>
       </c>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="23"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="29"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="31" customHeight="1" spans="1:16">
-      <c r="A9" s="18">
+      <c r="A9" s="23">
         <v>6</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="21"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="22"/>
-      <c r="P9" s="23"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="29"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="31" customHeight="1" spans="1:16">
-      <c r="A10" s="18">
+      <c r="A10" s="23">
         <v>7</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="21"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="23"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="29"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="31" customHeight="1" spans="1:16">
-      <c r="A11" s="18">
+      <c r="A11" s="23">
         <v>8</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="21"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="23"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="29"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="31" customHeight="1" spans="1:16">
-      <c r="A12" s="18">
+      <c r="A12" s="23">
         <v>9</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="26">
         <v>46266</v>
       </c>
-      <c r="F12" s="21"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="21">
+      <c r="F12" s="27"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="27">
         <v>46280</v>
       </c>
-      <c r="J12" s="21"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="23"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="29"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="31" customHeight="1" spans="1:16">
-      <c r="A13" s="18">
+      <c r="A13" s="23">
         <v>10</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="26">
         <v>46266</v>
       </c>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="21">
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="27">
         <v>46275</v>
       </c>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="23"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="28"/>
+      <c r="P13" s="29"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="31" customHeight="1" spans="1:16">
-      <c r="A14" s="18">
+      <c r="A14" s="23">
         <v>11</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="26">
         <v>46266</v>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="21">
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="27">
         <v>46275</v>
       </c>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="22"/>
-      <c r="P14" s="23"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="29"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="31" customHeight="1" spans="1:16">
-      <c r="A15" s="24">
+      <c r="A15" s="30">
         <v>12</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="26">
         <v>46266</v>
       </c>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="21">
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="27">
         <v>46275</v>
       </c>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="25"/>
-      <c r="N15" s="25"/>
-      <c r="O15" s="26"/>
-      <c r="P15" s="27"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="33"/>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A16" s="28"/>
+      <c r="A16" s="34"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A17" s="29"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="29"/>
+      <c r="A17" s="36"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="32" customHeight="1" spans="1:10">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
     </row>
     <row r="20" s="1" customFormat="1" ht="32" customHeight="1" spans="1:10">
-      <c r="A20" s="32" t="s">
+      <c r="A20" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="33" t="s">
+      <c r="E20" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="34"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="33" t="s">
+      <c r="F20" s="45"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="I20" s="34"/>
-      <c r="J20" s="35"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="46"/>
     </row>
     <row r="21" s="1" customFormat="1" ht="32" customHeight="1" spans="1:10">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36" t="s">
+      <c r="A21" s="47"/>
+      <c r="B21" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="36" t="s">
+      <c r="D21" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="37" t="s">
+      <c r="E21" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="F21" s="38"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="37"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="39"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="51"/>
     </row>
     <row r="22" s="1" customFormat="1" ht="32" customHeight="1" spans="1:10">
-      <c r="A22" s="36"/>
-      <c r="B22" s="36" t="s">
+      <c r="A22" s="47"/>
+      <c r="B22" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="25" t="s">
+      <c r="C22" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="D22" s="36" t="s">
+      <c r="D22" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="37" t="s">
+      <c r="E22" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="38"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="39"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="51"/>
     </row>
     <row r="23" s="1" customFormat="1" ht="32" customHeight="1" spans="1:10">
-      <c r="A23" s="36"/>
-      <c r="B23" s="36" t="s">
+      <c r="A23" s="47"/>
+      <c r="B23" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="C23" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="36" t="s">
+      <c r="D23" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="37" t="s">
+      <c r="E23" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="F23" s="38"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="37" t="s">
+      <c r="F23" s="50"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="I23" s="38"/>
-      <c r="J23" s="39"/>
+      <c r="I23" s="50"/>
+      <c r="J23" s="51"/>
     </row>
     <row r="24" s="1" customFormat="1" ht="32" customHeight="1" spans="1:10">
-      <c r="A24" s="36"/>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="37"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="39"/>
+      <c r="A24" s="47"/>
+      <c r="B24" s="47"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="51"/>
     </row>
     <row r="25" s="1" customFormat="1" ht="32" customHeight="1" spans="1:10">
-      <c r="A25" s="36"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="39"/>
+      <c r="A25" s="47"/>
+      <c r="B25" s="47"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="50"/>
+      <c r="J25" s="51"/>
     </row>
     <row r="26" ht="32" customHeight="1"/>
   </sheetData>
@@ -2877,20 +2940,20 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation sqref="E4:L4 E5 F5 G5:L5 E6 F6:K6 L6 E7 F7:K7 L7 E8:H8 I8 J8:L8 E9 F9:L9 E10 F10:L10 E11 F11:L11 E12 F12:H12 I12 J12:L12 E13 F13:G13 H13 I13:L13 E14 F14:G14 H14 I14:L14 E15 F15:G15 H15 I15:L15 E23:F23 E16:F17 E24:F25 E19:F22"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B10 B11 B12 B19 B4:B9 B13:B16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B19 B4:B16">
       <formula1>"纸机安装,制浆安装,造纸安装,工艺技术,机修,电气仪表,土建,热电站,污水处理"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C10 C11 C12 C19 C21 C22 C23 C4:C9 C13:C16">
+    <dataValidation type="list" allowBlank="1" sqref="C19 C4:C16 C21:C23">
       <formula1>"土建工程,安装工程,设备采购,图纸设计,其他"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="输入错误" error="请输入0到100之间的整数" sqref="M10 M11 M12 G23 G16:G17 G19:G22 G24:G25 M4:M9 M13:M15">
+    <dataValidation type="whole" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="输入错误" error="请输入0到100之间的整数" sqref="G16:G17 G19:G25 M4:M15">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N10 N11 N12 N4:N9 N13:N15">
+    <dataValidation type="list" allowBlank="1" sqref="N4:N15">
       <formula1>"未开始,进行中,已完成,滞后"</formula1>
     </dataValidation>
+    <dataValidation sqref="E4:L15 E16:F17 E19:F25"/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
